--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_304_Greenland_Denmark.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_304_Greenland_Denmark.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re98dcff94894434e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1d0bdf0015044b45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R01d9097208694f77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R37a8c27759e140a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8c9622e15ff2461a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rc1cf0f932b5949ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R8f0a28e363d14be8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R24f47ec46a744110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R783bac5d519d483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R1e659211b36a44ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R86b7c368c99b46f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R6df6d57206684e36"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ304CommercialTable" displayName="EEZ304CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ304CommercialTable" displayName="EEZ304CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ304FunctionalTable" displayName="EEZ304FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ304FunctionalTable" displayName="EEZ304FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ304ValidationTable" displayName="EEZ304ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ304ValidationTable" displayName="EEZ304ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4312,7 +4266,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7ee5f92420d4315"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72ea1e09f9fb45d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4322,20 +4276,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4343,606 +4287,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>51528.8517995942</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.088830850045582</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1226.961258558006</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>51528.8517995942</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1228.8926605607023</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$55,A2,'Species'!$U$2:$U$55))</x:f>
-        <x:v>63323427.78364146</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.088830850045582</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1226.961258558006</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>63223904.85607907</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>99522.9275623858</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0015741344636802</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0015741344636801015</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>69979.77280095138</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.0894277324388786</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>122.86487197061314</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>69979.77280095138</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>127.14199631029696</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$55,A3,'Species'!$U$2:$U$55))</x:f>
-        <x:v>8897368.01525398</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.0894277324388786</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>122.86487197061314</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>8598055.825721487</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>299312.1895324923</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.034811612717969</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.03481161271796885</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>62544.5012420773</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.379871964582096</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2398.1258174586383</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>62544.5012420773</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2398.358683507852</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$55,A4,'Species'!$U$2:$U$55))</x:f>
-        <x:v>150004147.65960374</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.379871964582096</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2398.1258174586383</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>149989583.16869944</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>14564.490904301405</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0000971033494235</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.00009710334942340711</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>173.06630174129998</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3799911043619213</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>239.87837843152633</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>173.06630174129998</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>239.87943688358797</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$55,A5,'Species'!$U$2:$U$55))</x:f>
-        <x:v>41515.04700522816</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3799911043619213</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>239.87837843152633</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>41514.86382284428</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0.1831823838801938</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.000004412452963</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.00000441245296291673</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1.7836876029</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.2285395270154007</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>16.925422830053744</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1.7836876029</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>17.010674462279063</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$55,A6,'Species'!$U$2:$U$55))</x:f>
-        <x:v>30.341729155334786</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.2285395270154007</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>16.925422830053744</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>30.189666875807497</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0.15206227952728923</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0050368982259008</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.005036898225900744</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>58845.2307666307</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.2801600111205063</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>190.6162893772032</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>58845.2307666307</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>190.68794381212368</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$55,A7,'Species'!$U$2:$U$55))</x:f>
-        <x:v>11221076.058038726</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.2801600111205063</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>190.6162893772032</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>11216859.536280379</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4216.52175834775</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0003759092948172</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00037590929481728984</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>475.3986311555</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5229134118961314</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>333.35994200622616</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>475.3986311555</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>346.8203582326522</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$55,A8,'Species'!$U$2:$U$55))</x:f>
-        <x:v>164877.923560663</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5229134118961314</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>333.35994200622616</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>158478.86011183678</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>6399.063448826229</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0403780254622634</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.04037802546226343</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>890.3911191613</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.228707303269572</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>169.31962707357692</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>890.3911191613</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>310.9320279653327</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$55,A9,'Species'!$U$2:$U$55))</x:f>
-        <x:v>276851.1163631452</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.228707303269572</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>169.31962707357692</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>150760.69224601611</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>126090.42411712906</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.8363614032188886</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.8363614032188886</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>17620.1570140036</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.876271414762126</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>752.0927717549185</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>17620.1570140036</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>791.1113422561896</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$55,A10,'Species'!$U$2:$U$55))</x:f>
-        <x:v>13939506.0661132</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.876271414762126</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>752.0927717549185</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>13251992.727418836</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>687513.3386943638</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0518799966794334</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.05187999667943333</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>226.9307748866</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.153965951648782</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1425.4958314514247</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>226.9307748866</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1448.7203448068906</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$55,A11,'Species'!$U$2:$U$55))</x:f>
-        <x:v>328759.23044101003</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.153965951648782</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1425.4958314514247</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>323488.87362888997</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>5270.356812120066</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.016292235194977</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.01629223519497699</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68f82084693d4eb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e6725ab77584670"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4952,20 +4502,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4973,984 +4513,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>18.8827856387</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.81</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>645.6542290346556</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>18.8827856387</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>645.6542290346556</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$55,A2,'Species'!$U$2:$U$55))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>12191.750403581515</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.81</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>645.6542290346556</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>12191.750403581515</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>85.4515530201</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.5400000000000005</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>346.736850452532</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>85.4515530201</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$55,A3,'Species'!$U$2:$U$55))</x:f>
-        <x:v>29629.202360466992</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.5400000000000005</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>346.736850452532</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>29629.20236046702</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>-2.9103830456733704e-11</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>-9.822684425540156e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>51397.5043526967</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.089804706129559</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1229.715666992271</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>51397.5043526967</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1230.965750019265</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$55,A4,'Species'!$U$2:$U$55))</x:f>
-        <x:v>63268567.49463572</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.089804706129559</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1229.715666992271</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>63204316.34681457</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>64251.14782115072</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0010165626579772</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0010165626579772176</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>466.62524152350005</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.6412587895791817</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>437.78289572268454</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>466.62524152350005</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>595.0913454879061</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$55,A5,'Species'!$U$2:$U$55))</x:f>
-        <x:v>277684.6428168388</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.6412587895791817</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>437.78289572268454</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>204280.54945145492</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>73404.09336538389</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.3593298214758698</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.3593298214758698</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>19.4910816751</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.999987715857848</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>999.9717151174256</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>19.4910816751</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>999.9864205462835</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$55,A6,'Species'!$U$2:$U$55))</x:f>
-        <x:v>19490.816996858506</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.999987715857848</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>999.9717151174256</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>19490.53037214357</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0.2866247149358969</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.000014705844811</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.000014705844810952362</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.1415957789</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6404602798650236</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>436.9787116110333</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.1415957789</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>444.12308760361</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$55,A7,'Species'!$U$2:$U$55))</x:f>
-        <x:v>62.885954516706086</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6404602798650236</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>436.9787116110333</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>61.87434103328273</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1.0116134834233534</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.01634948294446</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.016349482944459932</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>193.7133382738</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.79</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>616.5950018614822</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>193.7133382738</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$55,A8,'Species'!$U$2:$U$55))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>119442.67617352762</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.79</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>119442.67617352762</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>226.78917910770002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.154286558812897</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1426.54855703268</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>226.78917910770002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1449.3475649047548</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$55,A9,'Species'!$U$2:$U$55))</x:f>
-        <x:v>328696.3444864933</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.154286558812897</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1426.54855703268</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>323525.7762067155</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>5170.568279777828</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.015981936093012</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.015981936093011996</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2971.700896484</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.538374500129647</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>345.44149149853695</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2971.700896484</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>346.20609684610076</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$55,A10,'Species'!$U$2:$U$55))</x:f>
-        <x:v>1028820.9683657843</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.538374500129647</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>345.44149149853695</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1026548.7899689723</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2272.1783968119416</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0022134149092714</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0022134149092715005</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>4199.6259336021</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.65</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>446.683592150963</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>4199.6259336021</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>446.683592150963</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$55,A11,'Species'!$U$2:$U$55))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1875903.9977117279</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.65</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>446.683592150963</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>1875903.9977117279</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>13244.0603828791</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.9498065328030503</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>890.8539968242176</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>13244.0603828791</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>904.4987758519193</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$55,A12,'Species'!$U$2:$U$55))</x:f>
-        <x:v>11979236.403623048</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.9498065328030503</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>890.8539968242176</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>11798524.126269124</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>180712.27735392377</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0153165154743018</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.015316515474301766</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>58916.6865242226</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.28044562022168</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>190.74168736126103</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>58916.6865242226</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>190.8588658287059</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$55,A13,'Species'!$U$2:$U$55))</x:f>
-        <x:v>11244771.968398524</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.28044562022168</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>190.74168736126103</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>11237868.201364687</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>6903.767033837736</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0006143306639776</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0006143306639776543</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>173.0733007586</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.38005418470656</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>239.91322278342048</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>173.0733007586</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>239.95463255108484</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$55,A14,'Species'!$U$2:$U$55))</x:f>
-        <x:v>41529.74028793326</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.38005418470656</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>239.91322278342048</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>41522.57336275994</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>7.166925173318305</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0001726031070066</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.00017260310700651456</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1.7836876029</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.2285395270154007</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>16.925422830053744</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1.7836876029</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>17.010674462279063</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$55,A15,'Species'!$U$2:$U$55))</x:f>
-        <x:v>30.341729155334786</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.2285395270154007</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>16.925422830053744</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>30.189666875807497</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0.15206227952728923</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0050368982259008</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.005036898225900744</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>67008.07190446739</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.0695176607997134</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>117.35934062767254</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>67008.07190446739</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>117.42685356036347</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$55,A16,'Species'!$U$2:$U$55))</x:f>
-        <x:v>7868547.046888198</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.0695176607997134</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>117.35934062767254</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>7864023.135439962</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>4523.9114482356235</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.00057526680305</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.0005752668030499795</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>837.4722196714</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.150000083559634</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>141.25378163994776</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>837.4722196714</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>141.25378195525508</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$55,A17,'Species'!$U$2:$U$55))</x:f>
-        <x:v>118296.11831104741</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.150000083559634</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>141.25378163994776</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>118296.1180469863</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0.0002640611055539921</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0000000022322044</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>2.232204318396222e-9</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>62525.0101604022</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>4.379990386872632</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>2398.7798213354818</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>62525.0101604022</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>2398.794601677552</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$55,A18,'Species'!$U$2:$U$55))</x:f>
-        <x:v>149984656.84260687</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>4.379990386872632</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>2398.7798213354818</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>149983732.70156875</x:v>
       </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>924.1410381197929</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0000061616084723</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.000006161608472290855</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra28469896473411e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac9e51ca2b0d4d75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6125,7 +5026,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6224,7 +5125,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>248197559.24175033</x:v>
+        <x:v>246954669.5936757</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6238,7 +5139,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>248197559.2417503</x:v>
+        <x:v>247859388.53952336</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6252,7 +5153,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>8.940696716308594e-8</x:v>
+        <x:v>-1242889.6480745375</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6266,7 +5167,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>5.960464477539063e-8</x:v>
+        <x:v>-338170.7022268772</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6277,9 +5178,9 @@
         <x:v>EEZ_304</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6291,47 +5192,19 @@
         <x:v>EEZ_304</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_304</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_304</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7209a001a8b425d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8653fb797ea244ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6378,7 +5251,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
